--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/CALIFORNIA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/CALIFORNIA_2010.xlsx
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C197">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C259">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C293">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C918">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1139">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1140">
@@ -22560,7 +22560,7 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1234">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1235">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1246">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1410">
@@ -27726,7 +27726,7 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C1521">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="B1870" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1870">
@@ -34908,7 +34908,7 @@
       </c>
       <c r="B1920" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1920">
@@ -38292,7 +38292,7 @@
       </c>
       <c r="B2108" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C2108">
